--- a/Sedes_a_priorizar_UhWalaVixc_1.xlsx
+++ b/Sedes_a_priorizar_UhWalaVixc_1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,11 +450,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>219473006717</v>
+        <v>219473000701</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA BELEN</t>
+          <t>ESCUELA RURAL MIXTA LOMITAS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,34 +473,62 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>46.36631525862069</v>
+        <v>45.56404163793103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>219473006717</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ESCUELA RURAL MIXTA BELEN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZONA UH WALA VXIC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HONDURAS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>46.36631525862069</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>219473000531</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ESCUELA RURAL MIXTA PUEBLILLO</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>ZONA UH WALA VXIC</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>HONDURAS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>MORALES</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>47.04923155172413</v>
       </c>
     </row>
